--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.07874942570135</v>
+        <v>8.46279678167647</v>
       </c>
       <c r="D2" t="n">
-        <v>9.516235827839997</v>
+        <v>1.546388322024</v>
       </c>
       <c r="E2" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F2" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>91.27403322372287</v>
+        <v>14.83203039885497</v>
       </c>
       <c r="D3" t="n">
-        <v>43.50615575190938</v>
+        <v>7.069750309685274</v>
       </c>
       <c r="E3" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F3" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.54648948687256</v>
+        <v>10.97630454161679</v>
       </c>
       <c r="D4" t="n">
-        <v>28.46049894151541</v>
+        <v>4.624831077996255</v>
       </c>
       <c r="E4" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F4" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.45781937135274</v>
+        <v>6.736895647844821</v>
       </c>
       <c r="D5" t="n">
-        <v>25.81331362870383</v>
+        <v>4.194663464664373</v>
       </c>
       <c r="E5" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F5" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.45824418443321</v>
+        <v>8.361964679970397</v>
       </c>
       <c r="D6" t="n">
-        <v>32.17530108639234</v>
+        <v>5.228486426538755</v>
       </c>
       <c r="E6" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F6" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.35014932061924</v>
+        <v>9.156899264600627</v>
       </c>
       <c r="D7" t="n">
-        <v>18.46060085110406</v>
+        <v>2.99984763830441</v>
       </c>
       <c r="E7" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F7" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.6626234931971</v>
+        <v>6.445176317644528</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04931744480268</v>
+        <v>5.370514084780436</v>
       </c>
       <c r="E8" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F8" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.22746975509037</v>
+        <v>4.586963835202185</v>
       </c>
       <c r="D9" t="n">
-        <v>25.30063391989301</v>
+        <v>4.111353011982613</v>
       </c>
       <c r="E9" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F9" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.54157123914564</v>
+        <v>4.800505326361167</v>
       </c>
       <c r="D10" t="n">
-        <v>16.46788369389241</v>
+        <v>2.676031100257517</v>
       </c>
       <c r="E10" t="n">
-        <v>18.63152884106104</v>
+        <v>3.02762343667242</v>
       </c>
       <c r="F10" t="n">
-        <v>9.545885463467982</v>
+        <v>1.551206387813547</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
